--- a/artfynd/A 64483-2023 artfynd.xlsx
+++ b/artfynd/A 64483-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123419567</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 64483-2023 artfynd.xlsx
+++ b/artfynd/A 64483-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123419567</v>
       </c>
       <c r="B2" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 64483-2023 artfynd.xlsx
+++ b/artfynd/A 64483-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123419567</v>
       </c>
       <c r="B2" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 64483-2023 artfynd.xlsx
+++ b/artfynd/A 64483-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419567</v>
+        <v>123419563</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,16 +708,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gammelbodberget, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599889</v>
+        <v>599992</v>
       </c>
       <c r="R2" t="n">
-        <v>6913361</v>
+        <v>6913349</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2112</t>
+          <t>2024_2116</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spår av födosök</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,6 +793,507 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123419569</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gammelbodberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>599854</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6913369</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2024_2110</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann, Tove von Euler</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123419566</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gammelbodberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>599879</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6913349</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2024_2113</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann, Tove von Euler</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>119261848</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gammelbodberget, Gammelbodberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>599888</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6913351</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spår på tall vid snitslad yta av SCA</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123419567</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gammelbodberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>599889</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6913361</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2024_2112</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spår av födosök</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>

--- a/artfynd/A 64483-2023 artfynd.xlsx
+++ b/artfynd/A 64483-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123419563</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,6 +932,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123419569</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1047,6 +1062,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123419566</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1173,6 +1193,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119261848</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1298,8 +1323,20 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123419567</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>